--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123836462</v>
+        <v>123841770</v>
       </c>
       <c r="B2" t="n">
-        <v>97367</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604732</v>
+        <v>604701</v>
       </c>
       <c r="R2" t="n">
-        <v>6529398</v>
+        <v>6529370</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,49 +760,45 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123836465</v>
+        <v>123836462</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>97367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,32 +807,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604714</v>
+        <v>604732</v>
       </c>
       <c r="R3" t="n">
-        <v>6529365</v>
+        <v>6529398</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123841770</v>
+        <v>123836449</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>57643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,53 +923,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604701</v>
+        <v>604638</v>
       </c>
       <c r="R4" t="n">
-        <v>6529370</v>
+        <v>6529269</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,35 +992,39 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123836466</v>
+        <v>123836465</v>
       </c>
       <c r="B6" t="n">
         <v>98502</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604643</v>
+        <v>604714</v>
       </c>
       <c r="R6" t="n">
-        <v>6529349</v>
+        <v>6529365</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836449</v>
+        <v>123836466</v>
       </c>
       <c r="B8" t="n">
-        <v>57643</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,35 +1398,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604638</v>
+        <v>604643</v>
       </c>
       <c r="R8" t="n">
-        <v>6529269</v>
+        <v>6529349</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,6 +1503,788 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123889049</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91452</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Husby Skans 9 1300 m s, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>604560</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6529321</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby-Oppunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123885069</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Husby Skans 4 1200 m s, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>604718</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6529373</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby-Oppunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123887538</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Husby Skans 1300 m s, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>604585</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6529358</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby-Oppunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123884604</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Husby Skans 3 1200 s, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>604647</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6529367</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby-Oppunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123885474</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Husby Skans 5 1200 m s, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>604718</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6529352</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby-Oppunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123886889</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Husby Skans 7 1200 m s, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>604613</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6529272</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby-Oppunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123841770</v>
+        <v>123836467</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,14 +710,10 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604701</v>
+        <v>604667</v>
       </c>
       <c r="R2" t="n">
-        <v>6529370</v>
+        <v>6529377</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,35 +756,39 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>123836462</v>
       </c>
       <c r="B3" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123836449</v>
+        <v>123841770</v>
       </c>
       <c r="B4" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,49 +923,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604638</v>
+        <v>604701</v>
       </c>
       <c r="R4" t="n">
-        <v>6529269</v>
+        <v>6529370</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,39 +996,35 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>123836450</v>
       </c>
       <c r="B5" t="n">
-        <v>91389</v>
+        <v>91391</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>123836465</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836467</v>
+        <v>123836466</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1310,14 +1310,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604667</v>
+        <v>604643</v>
       </c>
       <c r="R7" t="n">
-        <v>6529377</v>
+        <v>6529349</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836466</v>
+        <v>123836449</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,35 +1398,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604643</v>
+        <v>604638</v>
       </c>
       <c r="R8" t="n">
-        <v>6529349</v>
+        <v>6529269</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123889049</v>
+        <v>123884604</v>
       </c>
       <c r="B9" t="n">
-        <v>91452</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,49 +1518,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 3 1200 s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604560</v>
+        <v>604647</v>
       </c>
       <c r="R9" t="n">
-        <v>6529321</v>
+        <v>6529367</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1593,11 +1602,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123885069</v>
+        <v>123885474</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,17 +1695,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>604718</v>
       </c>
       <c r="R10" t="n">
-        <v>6529373</v>
+        <v>6529352</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1768,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123887538</v>
+        <v>123885069</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,7 +1807,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1824,17 +1828,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604585</v>
+        <v>604718</v>
       </c>
       <c r="R11" t="n">
-        <v>6529358</v>
+        <v>6529373</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1864,11 +1868,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123884604</v>
+        <v>123886889</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>91010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1918,58 +1917,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 3 1200 s, Srm</t>
+          <t>Husby Skans 7 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604647</v>
+        <v>604613</v>
       </c>
       <c r="R12" t="n">
-        <v>6529367</v>
+        <v>6529272</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2039,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123885474</v>
+        <v>123889049</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>91454</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2051,58 +2033,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604718</v>
+        <v>604560</v>
       </c>
       <c r="R13" t="n">
-        <v>6529352</v>
+        <v>6529321</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2135,6 +2108,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2172,10 +2150,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123886889</v>
+        <v>123887538</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2184,41 +2162,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 7 1200 m s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604613</v>
+        <v>604585</v>
       </c>
       <c r="R14" t="n">
-        <v>6529272</v>
+        <v>6529358</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2251,6 +2246,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123836467</v>
+        <v>123841770</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,10 +710,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604667</v>
+        <v>604701</v>
       </c>
       <c r="R2" t="n">
-        <v>6529377</v>
+        <v>6529370</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,39 +760,35 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -798,7 +798,7 @@
         <v>123836462</v>
       </c>
       <c r="B3" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123841770</v>
+        <v>123836466</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,30 +946,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604701</v>
+        <v>604643</v>
       </c>
       <c r="R4" t="n">
-        <v>6529370</v>
+        <v>6529349</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,45 +992,49 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123836450</v>
+        <v>123836467</v>
       </c>
       <c r="B5" t="n">
-        <v>91391</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,44 +1043,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604582</v>
+        <v>604667</v>
       </c>
       <c r="R5" t="n">
-        <v>6529290</v>
+        <v>6529377</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123836465</v>
+        <v>123836450</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>91391</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,35 +1163,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604714</v>
+        <v>604582</v>
       </c>
       <c r="R6" t="n">
-        <v>6529365</v>
+        <v>6529290</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836466</v>
+        <v>123836465</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604643</v>
+        <v>604714</v>
       </c>
       <c r="R7" t="n">
-        <v>6529349</v>
+        <v>6529365</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1509,7 +1509,7 @@
         <v>123884604</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123885474</v>
+        <v>123886889</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,58 +1651,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 7 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604718</v>
+        <v>604613</v>
       </c>
       <c r="R10" t="n">
-        <v>6529352</v>
+        <v>6529272</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1772,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123885069</v>
+        <v>123889049</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>91454</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1784,61 +1767,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604718</v>
+        <v>604560</v>
       </c>
       <c r="R11" t="n">
-        <v>6529373</v>
+        <v>6529321</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,6 +1842,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,17 +1877,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123886889</v>
+        <v>123885069</v>
       </c>
       <c r="B12" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1917,44 +1896,61 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 7 1200 m s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604613</v>
+        <v>604718</v>
       </c>
       <c r="R12" t="n">
-        <v>6529272</v>
+        <v>6529373</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2021,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123889049</v>
+        <v>123887538</v>
       </c>
       <c r="B13" t="n">
-        <v>91454</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,49 +2029,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604560</v>
+        <v>604585</v>
       </c>
       <c r="R13" t="n">
-        <v>6529321</v>
+        <v>6529358</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2112,7 +2117,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på grov granlåga</t>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2150,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123887538</v>
+        <v>123885474</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2185,7 +2190,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2206,14 +2211,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604585</v>
+        <v>604718</v>
       </c>
       <c r="R14" t="n">
-        <v>6529358</v>
+        <v>6529352</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2246,11 +2251,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836465</v>
+        <v>123836449</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,35 +1278,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604714</v>
+        <v>604638</v>
       </c>
       <c r="R7" t="n">
-        <v>6529365</v>
+        <v>6529269</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836449</v>
+        <v>123836465</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,35 +1398,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604638</v>
+        <v>604714</v>
       </c>
       <c r="R8" t="n">
-        <v>6529269</v>
+        <v>6529365</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123841770</v>
+        <v>123836462</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604701</v>
+        <v>604732</v>
       </c>
       <c r="R2" t="n">
-        <v>6529370</v>
+        <v>6529398</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,45 +752,49 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123836462</v>
+        <v>123841770</v>
       </c>
       <c r="B3" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,45 +803,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604732</v>
+        <v>604701</v>
       </c>
       <c r="R3" t="n">
-        <v>6529398</v>
+        <v>6529370</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,49 +876,45 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123836466</v>
+        <v>123836450</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>91391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,35 +923,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604643</v>
+        <v>604582</v>
       </c>
       <c r="R4" t="n">
-        <v>6529349</v>
+        <v>6529290</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1151,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123836450</v>
+        <v>123836449</v>
       </c>
       <c r="B6" t="n">
-        <v>91391</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,30 +1158,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604582</v>
+        <v>604638</v>
       </c>
       <c r="R6" t="n">
-        <v>6529290</v>
+        <v>6529269</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836449</v>
+        <v>123836465</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,35 +1278,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604638</v>
+        <v>604714</v>
       </c>
       <c r="R7" t="n">
-        <v>6529269</v>
+        <v>6529365</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,7 +1386,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836465</v>
+        <v>123836466</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604714</v>
+        <v>604643</v>
       </c>
       <c r="R8" t="n">
-        <v>6529365</v>
+        <v>6529349</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123884604</v>
+        <v>123887538</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1562,14 +1562,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 3 1200 s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604647</v>
+        <v>604585</v>
       </c>
       <c r="R9" t="n">
-        <v>6529367</v>
+        <v>6529358</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1602,6 +1602,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,10 +1644,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123886889</v>
+        <v>123889049</v>
       </c>
       <c r="B10" t="n">
-        <v>91010</v>
+        <v>91454</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,37 +1660,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>5467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husby Skans 7 1200 m s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604613</v>
+        <v>604560</v>
       </c>
       <c r="R10" t="n">
-        <v>6529272</v>
+        <v>6529321</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1718,6 +1731,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123889049</v>
+        <v>123884604</v>
       </c>
       <c r="B11" t="n">
-        <v>91454</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,49 +1785,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 3 1200 s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604560</v>
+        <v>604647</v>
       </c>
       <c r="R11" t="n">
-        <v>6529321</v>
+        <v>6529367</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1844,11 +1871,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1877,14 +1899,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123885069</v>
+        <v>123885474</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1940,17 +1962,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>604718</v>
       </c>
       <c r="R12" t="n">
-        <v>6529373</v>
+        <v>6529352</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2017,10 +2039,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123887538</v>
+        <v>123886889</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2029,58 +2051,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 7 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604585</v>
+        <v>604613</v>
       </c>
       <c r="R13" t="n">
-        <v>6529358</v>
+        <v>6529272</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2113,11 +2118,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2155,7 +2155,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123885474</v>
+        <v>123885069</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2211,17 +2211,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>604718</v>
       </c>
       <c r="R14" t="n">
-        <v>6529352</v>
+        <v>6529373</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123836462</v>
+        <v>123836465</v>
       </c>
       <c r="B2" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604732</v>
+        <v>604714</v>
       </c>
       <c r="R2" t="n">
-        <v>6529398</v>
+        <v>6529365</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123841770</v>
+        <v>123836449</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,53 +807,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604701</v>
+        <v>604638</v>
       </c>
       <c r="R3" t="n">
-        <v>6529370</v>
+        <v>6529269</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,45 +876,49 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123836450</v>
+        <v>123836467</v>
       </c>
       <c r="B4" t="n">
-        <v>91391</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,44 +927,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604582</v>
+        <v>604667</v>
       </c>
       <c r="R4" t="n">
-        <v>6529290</v>
+        <v>6529377</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123836467</v>
+        <v>123836462</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,46 +1047,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604667</v>
+        <v>604732</v>
       </c>
       <c r="R5" t="n">
-        <v>6529377</v>
+        <v>6529398</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123836449</v>
+        <v>123841770</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,49 +1163,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604638</v>
+        <v>604701</v>
       </c>
       <c r="R6" t="n">
-        <v>6529269</v>
+        <v>6529370</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,49 +1236,45 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836465</v>
+        <v>123836450</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>91391</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,35 +1283,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604714</v>
+        <v>604582</v>
       </c>
       <c r="R7" t="n">
-        <v>6529365</v>
+        <v>6529290</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123887538</v>
+        <v>123885069</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,17 +1562,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604585</v>
+        <v>604718</v>
       </c>
       <c r="R9" t="n">
-        <v>6529358</v>
+        <v>6529373</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,11 +1602,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123889049</v>
+        <v>123884604</v>
       </c>
       <c r="B10" t="n">
-        <v>91454</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,49 +1651,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 3 1200 s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604560</v>
+        <v>604647</v>
       </c>
       <c r="R10" t="n">
-        <v>6529321</v>
+        <v>6529367</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1731,11 +1735,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,7 +1772,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123884604</v>
+        <v>123887538</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1829,14 +1828,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 3 1200 s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604647</v>
+        <v>604585</v>
       </c>
       <c r="R11" t="n">
-        <v>6529367</v>
+        <v>6529358</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1869,6 +1868,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123885474</v>
+        <v>123889049</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>91454</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1918,58 +1922,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604718</v>
+        <v>604560</v>
       </c>
       <c r="R12" t="n">
-        <v>6529352</v>
+        <v>6529321</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2002,6 +1997,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2155,7 +2155,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123885069</v>
+        <v>123885474</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2211,17 +2211,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>604718</v>
       </c>
       <c r="R14" t="n">
-        <v>6529373</v>
+        <v>6529352</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123836465</v>
+        <v>123836466</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604714</v>
+        <v>604643</v>
       </c>
       <c r="R2" t="n">
-        <v>6529365</v>
+        <v>6529349</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123836449</v>
+        <v>123836467</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,49 +807,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604638</v>
+        <v>604667</v>
       </c>
       <c r="R3" t="n">
-        <v>6529269</v>
+        <v>6529377</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123836467</v>
+        <v>123836462</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,46 +927,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604667</v>
+        <v>604732</v>
       </c>
       <c r="R4" t="n">
-        <v>6529377</v>
+        <v>6529398</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123836462</v>
+        <v>123836450</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
+        <v>91391</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,27 +1047,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604732</v>
+        <v>604582</v>
       </c>
       <c r="R5" t="n">
-        <v>6529398</v>
+        <v>6529290</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1271,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836450</v>
+        <v>123836465</v>
       </c>
       <c r="B7" t="n">
-        <v>91391</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,30 +1278,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604582</v>
+        <v>604714</v>
       </c>
       <c r="R7" t="n">
-        <v>6529290</v>
+        <v>6529365</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836466</v>
+        <v>123836449</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,35 +1398,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604643</v>
+        <v>604638</v>
       </c>
       <c r="R8" t="n">
-        <v>6529349</v>
+        <v>6529269</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123885069</v>
+        <v>123889049</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>91454</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,61 +1518,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604718</v>
+        <v>604560</v>
       </c>
       <c r="R9" t="n">
-        <v>6529373</v>
+        <v>6529321</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,6 +1593,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,7 +1628,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1772,7 +1768,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123887538</v>
+        <v>123885474</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1807,7 +1803,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1828,14 +1824,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604585</v>
+        <v>604718</v>
       </c>
       <c r="R11" t="n">
-        <v>6529358</v>
+        <v>6529352</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1868,11 +1864,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,10 +1901,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123889049</v>
+        <v>123885069</v>
       </c>
       <c r="B12" t="n">
-        <v>91454</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1922,52 +1913,61 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604560</v>
+        <v>604718</v>
       </c>
       <c r="R12" t="n">
-        <v>6529321</v>
+        <v>6529373</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1997,11 +1997,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2155,7 +2150,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123885474</v>
+        <v>123887538</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2190,7 +2185,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2211,14 +2206,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604718</v>
+        <v>604585</v>
       </c>
       <c r="R14" t="n">
-        <v>6529352</v>
+        <v>6529358</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2251,6 +2246,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123836466</v>
+        <v>123841770</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,26 +710,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604643</v>
+        <v>604701</v>
       </c>
       <c r="R2" t="n">
-        <v>6529349</v>
+        <v>6529370</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,49 +760,45 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123836467</v>
+        <v>123836450</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>91391</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,49 +807,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604667</v>
+        <v>604582</v>
       </c>
       <c r="R3" t="n">
-        <v>6529377</v>
+        <v>6529290</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123836462</v>
+        <v>123836449</v>
       </c>
       <c r="B4" t="n">
-        <v>96957</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,31 +922,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604732</v>
+        <v>604638</v>
       </c>
       <c r="R4" t="n">
-        <v>6529398</v>
+        <v>6529269</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123836450</v>
+        <v>123836467</v>
       </c>
       <c r="B5" t="n">
-        <v>91391</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,44 +1042,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604582</v>
+        <v>604667</v>
       </c>
       <c r="R5" t="n">
-        <v>6529290</v>
+        <v>6529377</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123841770</v>
+        <v>123836462</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,53 +1162,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604701</v>
+        <v>604732</v>
       </c>
       <c r="R6" t="n">
-        <v>6529370</v>
+        <v>6529398</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,42 +1227,46 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836465</v>
+        <v>123836466</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604714</v>
+        <v>604643</v>
       </c>
       <c r="R7" t="n">
-        <v>6529365</v>
+        <v>6529349</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836449</v>
+        <v>123836465</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,35 +1398,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604638</v>
+        <v>604714</v>
       </c>
       <c r="R8" t="n">
-        <v>6529269</v>
+        <v>6529365</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123889049</v>
+        <v>123886889</v>
       </c>
       <c r="B9" t="n">
-        <v>91454</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,45 +1522,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5467</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 7 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604560</v>
+        <v>604613</v>
       </c>
       <c r="R9" t="n">
-        <v>6529321</v>
+        <v>6529272</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1595,11 +1587,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1628,14 +1615,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123884604</v>
+        <v>123887538</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1691,14 +1678,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husby Skans 3 1200 s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604647</v>
+        <v>604585</v>
       </c>
       <c r="R10" t="n">
-        <v>6529367</v>
+        <v>6529358</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1731,6 +1718,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123885474</v>
+        <v>123884604</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1803,7 +1795,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1824,14 +1816,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 3 1200 s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604718</v>
+        <v>604647</v>
       </c>
       <c r="R11" t="n">
-        <v>6529352</v>
+        <v>6529367</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1901,7 +1893,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123885069</v>
+        <v>123885474</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1957,17 +1949,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>604718</v>
       </c>
       <c r="R12" t="n">
-        <v>6529373</v>
+        <v>6529352</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2034,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123886889</v>
+        <v>123885069</v>
       </c>
       <c r="B13" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2046,44 +2038,61 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Husby Skans 7 1200 m s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604613</v>
+        <v>604718</v>
       </c>
       <c r="R13" t="n">
-        <v>6529272</v>
+        <v>6529373</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2150,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123887538</v>
+        <v>123889049</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>91454</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2162,58 +2171,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604585</v>
+        <v>604560</v>
       </c>
       <c r="R14" t="n">
-        <v>6529358</v>
+        <v>6529321</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Husby Skans 9</t>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123836467</v>
+        <v>123836465</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604667</v>
+        <v>604714</v>
       </c>
       <c r="R2" t="n">
-        <v>6529377</v>
+        <v>6529365</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123841770</v>
+        <v>123836449</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,53 +807,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604701</v>
+        <v>604638</v>
       </c>
       <c r="R3" t="n">
-        <v>6529370</v>
+        <v>6529269</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,30 +876,34 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123836465</v>
+        <v>123836462</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,32 +927,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -963,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604714</v>
+        <v>604732</v>
       </c>
       <c r="R4" t="n">
-        <v>6529365</v>
+        <v>6529398</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123836449</v>
+        <v>123836466</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,35 +1043,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604638</v>
+        <v>604643</v>
       </c>
       <c r="R5" t="n">
-        <v>6529269</v>
+        <v>6529349</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1151,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123836466</v>
+        <v>123836467</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1190,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1199,14 +1195,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604643</v>
+        <v>604667</v>
       </c>
       <c r="R6" t="n">
-        <v>6529349</v>
+        <v>6529377</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836450</v>
+        <v>123841770</v>
       </c>
       <c r="B7" t="n">
-        <v>91413</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,44 +1283,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604582</v>
+        <v>604701</v>
       </c>
       <c r="R7" t="n">
-        <v>6529290</v>
+        <v>6529370</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,49 +1356,45 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836462</v>
+        <v>123836450</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>91413</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,27 +1407,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604732</v>
+        <v>604582</v>
       </c>
       <c r="R8" t="n">
-        <v>6529398</v>
+        <v>6529290</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123884604</v>
+        <v>123889049</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91476</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,58 +1518,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 3 1200 s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604647</v>
+        <v>604560</v>
       </c>
       <c r="R9" t="n">
-        <v>6529367</v>
+        <v>6529321</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1602,6 +1593,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1772,7 +1768,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123887538</v>
+        <v>123885474</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1807,7 +1803,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1828,14 +1824,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604585</v>
+        <v>604718</v>
       </c>
       <c r="R11" t="n">
-        <v>6529358</v>
+        <v>6529352</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1870,11 +1866,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Husby Skans 9</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1903,17 +1894,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123889049</v>
+        <v>123884604</v>
       </c>
       <c r="B12" t="n">
-        <v>91476</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1922,49 +1913,58 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 3 1200 s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604560</v>
+        <v>604647</v>
       </c>
       <c r="R12" t="n">
-        <v>6529321</v>
+        <v>6529367</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1997,11 +1997,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,7 +2034,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123885474</v>
+        <v>123887538</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2074,7 +2069,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2095,14 +2090,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604718</v>
+        <v>604585</v>
       </c>
       <c r="R13" t="n">
-        <v>6529352</v>
+        <v>6529358</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2135,6 +2130,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123836465</v>
+        <v>123836449</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604714</v>
+        <v>604638</v>
       </c>
       <c r="R2" t="n">
-        <v>6529365</v>
+        <v>6529269</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123836449</v>
+        <v>123836465</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,35 +807,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604638</v>
+        <v>604714</v>
       </c>
       <c r="R3" t="n">
-        <v>6529269</v>
+        <v>6529365</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123836462</v>
+        <v>123836466</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,28 +927,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -959,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604732</v>
+        <v>604643</v>
       </c>
       <c r="R4" t="n">
-        <v>6529398</v>
+        <v>6529349</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123836466</v>
+        <v>123836462</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,32 +1047,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604643</v>
+        <v>604732</v>
       </c>
       <c r="R5" t="n">
-        <v>6529349</v>
+        <v>6529398</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1151,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123836467</v>
+        <v>123841770</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1186,10 +1186,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1199,13 +1203,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604667</v>
+        <v>604701</v>
       </c>
       <c r="R6" t="n">
-        <v>6529377</v>
+        <v>6529370</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,49 +1236,45 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123841770</v>
+        <v>123836450</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91413</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,53 +1283,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604701</v>
+        <v>604582</v>
       </c>
       <c r="R7" t="n">
-        <v>6529370</v>
+        <v>6529290</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,45 +1347,49 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836450</v>
+        <v>123836467</v>
       </c>
       <c r="B8" t="n">
-        <v>91413</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,44 +1398,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604582</v>
+        <v>604667</v>
       </c>
       <c r="R8" t="n">
-        <v>6529290</v>
+        <v>6529377</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123889049</v>
+        <v>123885474</v>
       </c>
       <c r="B9" t="n">
-        <v>91476</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,49 +1518,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604560</v>
+        <v>604718</v>
       </c>
       <c r="R9" t="n">
-        <v>6529321</v>
+        <v>6529352</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1593,11 +1602,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1639,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123885069</v>
+        <v>123884604</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1670,7 +1674,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1691,17 +1695,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 3 1200 s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604718</v>
+        <v>604647</v>
       </c>
       <c r="R10" t="n">
-        <v>6529373</v>
+        <v>6529367</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1768,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123885474</v>
+        <v>123886889</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,58 +1784,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 7 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604718</v>
+        <v>604613</v>
       </c>
       <c r="R11" t="n">
-        <v>6529352</v>
+        <v>6529272</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1894,14 +1881,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123884604</v>
+        <v>123885069</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1936,7 +1923,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1957,17 +1944,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 3 1200 s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604647</v>
+        <v>604718</v>
       </c>
       <c r="R12" t="n">
-        <v>6529367</v>
+        <v>6529373</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2165,17 +2152,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123886889</v>
+        <v>123889049</v>
       </c>
       <c r="B14" t="n">
-        <v>91032</v>
+        <v>91476</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2188,37 +2175,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>5467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 7 1200 m s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604613</v>
+        <v>604560</v>
       </c>
       <c r="R14" t="n">
-        <v>6529272</v>
+        <v>6529321</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2251,6 +2246,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123836449</v>
+        <v>123836466</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604638</v>
+        <v>604643</v>
       </c>
       <c r="R2" t="n">
-        <v>6529269</v>
+        <v>6529349</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123836465</v>
+        <v>123836462</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,32 +807,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604714</v>
+        <v>604732</v>
       </c>
       <c r="R3" t="n">
-        <v>6529365</v>
+        <v>6529398</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123836466</v>
+        <v>123836450</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91413</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,35 +923,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604643</v>
+        <v>604582</v>
       </c>
       <c r="R4" t="n">
-        <v>6529349</v>
+        <v>6529290</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123836462</v>
+        <v>123836467</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,42 +1038,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klapparberget, Klapparberget, Srm</t>
+          <t>Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604732</v>
+        <v>604667</v>
       </c>
       <c r="R5" t="n">
-        <v>6529398</v>
+        <v>6529377</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123841770</v>
+        <v>123836449</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,53 +1158,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klapparberget, Srm</t>
+          <t>Klapparberget, Klapparberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604701</v>
+        <v>604638</v>
       </c>
       <c r="R6" t="n">
-        <v>6529370</v>
+        <v>6529269</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,45 +1227,49 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123836450</v>
+        <v>123836465</v>
       </c>
       <c r="B7" t="n">
-        <v>91413</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,30 +1278,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604582</v>
+        <v>604714</v>
       </c>
       <c r="R7" t="n">
-        <v>6529290</v>
+        <v>6529365</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,7 +1386,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123836467</v>
+        <v>123841770</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1421,10 +1421,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1434,13 +1438,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604667</v>
+        <v>604701</v>
       </c>
       <c r="R8" t="n">
-        <v>6529377</v>
+        <v>6529370</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,34 +1471,30 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123885474</v>
+        <v>123887538</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1562,14 +1562,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604718</v>
+        <v>604585</v>
       </c>
       <c r="R9" t="n">
-        <v>6529352</v>
+        <v>6529358</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1602,6 +1602,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,7 +1644,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123884604</v>
+        <v>123885474</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1674,7 +1679,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1695,14 +1700,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husby Skans 3 1200 s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604647</v>
+        <v>604718</v>
       </c>
       <c r="R10" t="n">
-        <v>6529367</v>
+        <v>6529352</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1765,17 +1770,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123886889</v>
+        <v>123889049</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>91476</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1788,37 +1793,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>5467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 7 1200 m s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604613</v>
+        <v>604560</v>
       </c>
       <c r="R11" t="n">
-        <v>6529272</v>
+        <v>6529321</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1851,6 +1864,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,7 +1906,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123885069</v>
+        <v>123884604</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1923,7 +1941,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1944,17 +1962,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 3 1200 s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604718</v>
+        <v>604647</v>
       </c>
       <c r="R12" t="n">
-        <v>6529373</v>
+        <v>6529367</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2021,7 +2039,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123887538</v>
+        <v>123885069</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2056,7 +2074,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2077,17 +2095,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604585</v>
+        <v>604718</v>
       </c>
       <c r="R13" t="n">
-        <v>6529358</v>
+        <v>6529373</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2117,11 +2135,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,17 +2165,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123889049</v>
+        <v>123886889</v>
       </c>
       <c r="B14" t="n">
-        <v>91476</v>
+        <v>91032</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2175,45 +2188,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5467</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 7 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604560</v>
+        <v>604613</v>
       </c>
       <c r="R14" t="n">
-        <v>6529321</v>
+        <v>6529272</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2246,11 +2251,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12931-2025 artfynd.xlsx
+++ b/artfynd/A 12931-2025 artfynd.xlsx
@@ -1506,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123887538</v>
+        <v>123886889</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,58 +1518,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husby Skans 1300 m s, Srm</t>
+          <t>Husby Skans 7 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604585</v>
+        <v>604613</v>
       </c>
       <c r="R9" t="n">
-        <v>6529358</v>
+        <v>6529272</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1602,11 +1585,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,7 +1622,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123885474</v>
+        <v>123885069</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1700,17 +1678,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husby Skans 5 1200 m s, Srm</t>
+          <t>Husby Skans 4 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>604718</v>
       </c>
       <c r="R10" t="n">
-        <v>6529352</v>
+        <v>6529373</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1770,17 +1748,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson, Bo Karlsson</t>
+          <t>Bo Karlsson, Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123889049</v>
+        <v>123885474</v>
       </c>
       <c r="B11" t="n">
-        <v>91476</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,49 +1767,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Husby Skans 9 1300 m s, Srm</t>
+          <t>Husby Skans 5 1200 m s, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604560</v>
+        <v>604718</v>
       </c>
       <c r="R11" t="n">
-        <v>6529321</v>
+        <v>6529352</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1864,11 +1851,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123884604</v>
+        <v>123889049</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1918,58 +1900,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Husby Skans 3 1200 s, Srm</t>
+          <t>Husby Skans 9 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604647</v>
+        <v>604560</v>
       </c>
       <c r="R12" t="n">
-        <v>6529367</v>
+        <v>6529321</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2002,6 +1975,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på grov granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,7 +2017,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123885069</v>
+        <v>123887538</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2074,7 +2052,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2095,17 +2073,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Husby Skans 4 1200 m s, Srm</t>
+          <t>Husby Skans 1300 m s, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604718</v>
+        <v>604585</v>
       </c>
       <c r="R13" t="n">
-        <v>6529373</v>
+        <v>6529358</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2135,6 +2113,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Husby Skans 9</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2172,10 +2155,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123886889</v>
+        <v>123884604</v>
       </c>
       <c r="B14" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2184,41 +2167,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Husby Skans 7 1200 m s, Srm</t>
+          <t>Husby Skans 3 1200 s, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604613</v>
+        <v>604647</v>
       </c>
       <c r="R14" t="n">
-        <v>6529272</v>
+        <v>6529367</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
